--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.0913635861031</v>
+        <v>6.677346582741754</v>
       </c>
       <c r="D2" t="n">
-        <v>40.58666828001604</v>
+        <v>6.595333595502607</v>
       </c>
       <c r="E2" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F2" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.84369367685209</v>
+        <v>2.087100222488464</v>
       </c>
       <c r="D3" t="n">
-        <v>12.95667773653205</v>
+        <v>2.105460132186459</v>
       </c>
       <c r="E3" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F3" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.85327592266109</v>
+        <v>3.226157337432427</v>
       </c>
       <c r="D4" t="n">
-        <v>19.8720782626766</v>
+        <v>3.229212717684947</v>
       </c>
       <c r="E4" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F4" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.37423367909135</v>
+        <v>3.960812972852344</v>
       </c>
       <c r="D5" t="n">
-        <v>25.74291811524456</v>
+        <v>4.183224193727241</v>
       </c>
       <c r="E5" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F5" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.25290299294891</v>
+        <v>7.191096736354198</v>
       </c>
       <c r="D6" t="n">
-        <v>39.86117011139966</v>
+        <v>6.477440143102445</v>
       </c>
       <c r="E6" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F6" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>14.23392273595201</v>
+        <v>2.313012444592202</v>
       </c>
       <c r="D7" t="n">
-        <v>12.67589332092205</v>
+        <v>2.059832664649833</v>
       </c>
       <c r="E7" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F7" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.48318307981035</v>
+        <v>2.841017250469181</v>
       </c>
       <c r="D8" t="n">
-        <v>16.93981938019409</v>
+        <v>2.75272064928154</v>
       </c>
       <c r="E8" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F8" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.31814481580845</v>
+        <v>2.976698532568874</v>
       </c>
       <c r="D9" t="n">
-        <v>19.13169324224762</v>
+        <v>3.108900151865238</v>
       </c>
       <c r="E9" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F9" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.59941462975983</v>
+        <v>1.884904877335972</v>
       </c>
       <c r="D10" t="n">
-        <v>12.70005205950155</v>
+        <v>2.063758459669002</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F10" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.89989250110502</v>
+        <v>4.371232531429565</v>
       </c>
       <c r="D11" t="n">
-        <v>27.12531090882098</v>
+        <v>4.407863022683409</v>
       </c>
       <c r="E11" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F11" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>15.79166342523015</v>
+        <v>2.5661453065999</v>
       </c>
       <c r="D12" t="n">
-        <v>15.24369405665778</v>
+        <v>2.477100284206889</v>
       </c>
       <c r="E12" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F12" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.00269624330865</v>
+        <v>3.575438139537656</v>
       </c>
       <c r="D13" t="n">
-        <v>21.32636981735937</v>
+        <v>3.465535095320898</v>
       </c>
       <c r="E13" t="n">
-        <v>10.07006150493976</v>
+        <v>1.636384994552711</v>
       </c>
       <c r="F13" t="n">
-        <v>9.329315229519604</v>
+        <v>1.516013724796936</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
